--- a/src/xlsx/dex.xlsx
+++ b/src/xlsx/dex.xlsx
@@ -529,6 +529,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
@@ -577,6 +578,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -655,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
@@ -703,6 +706,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -781,6 +785,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
@@ -829,6 +834,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -907,6 +913,7 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
@@ -955,6 +962,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -1033,6 +1041,7 @@
         </is>
       </c>
     </row>
+    <row r="46"/>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
@@ -1081,6 +1090,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -1159,6 +1169,7 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
@@ -1207,6 +1218,7 @@
         </is>
       </c>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
@@ -1237,7 +1249,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>透過從水面噴水來捕食。</t>
+          <t>在水中會朝獵物噴水。</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1271,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>在危急時刻會將四肢</t>
+          <t>危險時會把四肢</t>
         </is>
       </c>
     </row>
@@ -1281,10 +1293,11 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>縮入龜殼裡保護自己。</t>
-        </is>
-      </c>
-    </row>
+          <t>縮進龜殼裡保護自己。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
@@ -1333,6 +1346,7 @@
         </is>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
@@ -1385,7 +1399,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>它會把頭縮排殼裡，但尾巴</t>
+          <t>它會把頭縮進殼裡，</t>
         </is>
       </c>
     </row>
@@ -1407,10 +1421,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>還是會露出來一點點。</t>
-        </is>
-      </c>
-    </row>
+          <t>但尾巴還是會露出一點。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76"/>
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
@@ -1459,6 +1474,7 @@
         </is>
       </c>
     </row>
+    <row r="81"/>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
@@ -1511,7 +1527,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>它會以超越了</t>
+          <t>它噴出的水柱力道</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1549,11 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>消防水槍的力道來噴水。</t>
-        </is>
-      </c>
-    </row>
+          <t>比消防水管還要強。</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
@@ -1585,6 +1602,7 @@
         </is>
       </c>
     </row>
+    <row r="91"/>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
@@ -1663,6 +1681,7 @@
         </is>
       </c>
     </row>
+    <row r="96"/>
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
@@ -1711,6 +1730,7 @@
         </is>
       </c>
     </row>
+    <row r="101"/>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
@@ -1785,10 +1805,11 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>它的身體還是會被撞出來。</t>
-        </is>
-      </c>
-    </row>
+          <t>身體可能會從殼裡彈出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106"/>
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
@@ -1837,6 +1858,7 @@
         </is>
       </c>
     </row>
+    <row r="111"/>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
@@ -1915,6 +1937,7 @@
         </is>
       </c>
     </row>
+    <row r="116"/>
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
@@ -1963,6 +1986,7 @@
         </is>
       </c>
     </row>
+    <row r="121"/>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
@@ -2041,6 +2065,7 @@
         </is>
       </c>
     </row>
+    <row r="126"/>
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
@@ -2089,6 +2114,7 @@
         </is>
       </c>
     </row>
+    <row r="131"/>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -2141,7 +2167,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>但是如果遇到了危險，有時</t>
+          <t>但遇到危險時，有時會</t>
         </is>
       </c>
     </row>
@@ -2163,10 +2189,11 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>似乎會豎起毒刺來反抗。</t>
-        </is>
-      </c>
-    </row>
+          <t>伸出毒刺來反抗。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136"/>
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
@@ -2215,6 +2242,7 @@
         </is>
       </c>
     </row>
+    <row r="141"/>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
@@ -2245,7 +2273,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>它會用雙手</t>
+          <t>它會用前腳</t>
         </is>
       </c>
     </row>
@@ -2289,10 +2317,11 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>反覆刺傷敵人。</t>
-        </is>
-      </c>
-    </row>
+          <t>反覆刺擊敵人。</t>
+        </is>
+      </c>
+    </row>
+    <row r="146"/>
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
@@ -2341,6 +2370,7 @@
         </is>
       </c>
     </row>
+    <row r="151"/>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
@@ -2419,6 +2449,7 @@
         </is>
       </c>
     </row>
+    <row r="156"/>
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
@@ -2467,6 +2498,7 @@
         </is>
       </c>
     </row>
+    <row r="161"/>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
@@ -2497,7 +2529,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>擁有超群的體力，</t>
+          <t>充滿活力的寶可夢。</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2551,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>而且飛翔範圍廣，經常飛到</t>
+          <t>會在廣大的地盤裡飛行，</t>
         </is>
       </c>
     </row>
@@ -2541,10 +2573,11 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>很遠的地方尋找食物。</t>
-        </is>
-      </c>
-    </row>
+          <t>四處尋找獵物。</t>
+        </is>
+      </c>
+    </row>
+    <row r="166"/>
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
@@ -2593,6 +2626,7 @@
         </is>
       </c>
     </row>
+    <row r="171"/>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
@@ -2671,6 +2705,7 @@
         </is>
       </c>
     </row>
+    <row r="176"/>
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
@@ -2719,6 +2754,7 @@
         </is>
       </c>
     </row>
+    <row r="181"/>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
@@ -2749,7 +2785,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>有兩顆大門牙，見啥咬啥。</t>
+          <t>有兩顆大門牙，</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2807,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>只要看到１隻小拉達出沒，</t>
+          <t>見到什麼就咬什麼。</t>
         </is>
       </c>
     </row>
@@ -2793,10 +2829,11 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>附近必還住著４０隻以上。</t>
-        </is>
-      </c>
-    </row>
+          <t>附近還有４０隻以上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="186"/>
     <row r="187">
       <c r="B187" t="inlineStr">
         <is>
@@ -2845,6 +2882,7 @@
         </is>
       </c>
     </row>
+    <row r="191"/>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
@@ -2923,6 +2961,7 @@
         </is>
       </c>
     </row>
+    <row r="196"/>
     <row r="197">
       <c r="B197" t="inlineStr">
         <is>
@@ -2971,6 +3010,7 @@
         </is>
       </c>
     </row>
+    <row r="201"/>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
@@ -3001,7 +3041,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>不擅長高空飛行。會以</t>
+          <t>不擅長高空飛行。</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3063,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>超高速在地盤裡四處盤旋，</t>
+          <t>但會在領地裡高速飛行，</t>
         </is>
       </c>
     </row>
@@ -3045,10 +3085,11 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>以保護自己地盤不被侵犯。</t>
-        </is>
-      </c>
-    </row>
+          <t>保護地盤不被侵犯。</t>
+        </is>
+      </c>
+    </row>
+    <row r="206"/>
     <row r="207">
       <c r="B207" t="inlineStr">
         <is>
@@ -3097,6 +3138,7 @@
         </is>
       </c>
     </row>
+    <row r="211"/>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
@@ -3149,7 +3191,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>哪怕只察覺到一絲危險，</t>
+          <t>只要察覺到一絲危險，</t>
         </is>
       </c>
     </row>
@@ -3171,10 +3213,11 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>都會立即飛向高空。</t>
-        </is>
-      </c>
-    </row>
+          <t>就會立刻飛向高空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="216"/>
     <row r="217">
       <c r="B217" t="inlineStr">
         <is>
@@ -3223,6 +3266,7 @@
         </is>
       </c>
     </row>
+    <row r="221"/>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
@@ -3301,6 +3345,7 @@
         </is>
       </c>
     </row>
+    <row r="226"/>
     <row r="227">
       <c r="B227" t="inlineStr">
         <is>
@@ -3349,6 +3394,7 @@
         </is>
       </c>
     </row>
+    <row r="231"/>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
@@ -3401,7 +3447,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>它腹部那可怕的紋路大約有</t>
+          <t>它腹部那可怕的紋路</t>
         </is>
       </c>
     </row>
@@ -3423,10 +3469,11 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>６個種類已經得到確認。</t>
-        </is>
-      </c>
-    </row>
+          <t>目前已確認有６種。</t>
+        </is>
+      </c>
+    </row>
+    <row r="236"/>
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
@@ -3475,6 +3522,7 @@
         </is>
       </c>
     </row>
+    <row r="241"/>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
@@ -3505,7 +3553,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>會將尾巴豎起來來感覺周圍</t>
+          <t>會豎起尾巴感知周遭。</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3575,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>是否安全。所以如果隨便</t>
+          <t>如果隨便去拉它的尾巴，</t>
         </is>
       </c>
     </row>
@@ -3549,10 +3597,11 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>去拉它的尾巴，會被咬喔。</t>
-        </is>
-      </c>
-    </row>
+          <t>可是會被咬的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="246"/>
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
@@ -3601,6 +3650,7 @@
         </is>
       </c>
     </row>
+    <row r="251"/>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
@@ -3679,6 +3729,7 @@
         </is>
       </c>
     </row>
+    <row r="256"/>
     <row r="257">
       <c r="B257" t="inlineStr">
         <is>
@@ -3727,6 +3778,7 @@
         </is>
       </c>
     </row>
+    <row r="261"/>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
@@ -3805,6 +3857,7 @@
         </is>
       </c>
     </row>
+    <row r="266"/>
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
@@ -3853,6 +3906,7 @@
         </is>
       </c>
     </row>
+    <row r="271"/>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
@@ -3927,10 +3981,11 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>但到次日就會長出新的來。</t>
-        </is>
-      </c>
-    </row>
+          <t>但隔天就會長出新的來。</t>
+        </is>
+      </c>
+    </row>
+    <row r="276"/>
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
@@ -3979,6 +4034,7 @@
         </is>
       </c>
     </row>
+    <row r="281"/>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
@@ -4009,7 +4065,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>它性格溫順不喜歡戰鬥，</t>
+          <t>它性格溫順，不喜歡戰鬥。</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4087,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>但由於小犄角中含有毒液，</t>
+          <t>但小角會分泌毒液，</t>
         </is>
       </c>
     </row>
@@ -4053,10 +4109,11 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>請一定要小心提防。</t>
-        </is>
-      </c>
-    </row>
+          <t>所以一定要小心。</t>
+        </is>
+      </c>
+    </row>
+    <row r="286"/>
     <row r="287">
       <c r="B287" t="inlineStr">
         <is>
@@ -4105,6 +4162,7 @@
         </is>
       </c>
     </row>
+    <row r="291"/>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
@@ -4135,7 +4193,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>待在巢穴深處的時候，</t>
+          <t>待在巢穴深處時，</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4215,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>它必會把身上的刺收起來。</t>
+          <t>會收起身上的刺。</t>
         </is>
       </c>
     </row>
@@ -4179,10 +4237,11 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>這表明它正處於放鬆狀態。</t>
-        </is>
-      </c>
-    </row>
+          <t>這表示它正處於放鬆狀態。</t>
+        </is>
+      </c>
+    </row>
+    <row r="296"/>
     <row r="297">
       <c r="B297" t="inlineStr">
         <is>
@@ -4231,6 +4290,7 @@
         </is>
       </c>
     </row>
+    <row r="301"/>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
@@ -4305,10 +4365,11 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>會自己長出新的。</t>
-        </is>
-      </c>
-    </row>
+          <t>會週期性地長出新的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="306"/>
     <row r="307">
       <c r="B307" t="inlineStr">
         <is>
@@ -4357,6 +4418,7 @@
         </is>
       </c>
     </row>
+    <row r="311"/>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
@@ -4387,7 +4449,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>一直豎起它的大耳朵感知</t>
+          <t>總是豎起大耳朵</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4471,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>周圍的情形。當它察覺到</t>
+          <t>感知周圍的情形。察覺到</t>
         </is>
       </c>
     </row>
@@ -4431,10 +4493,11 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>危險便會使用毒針。</t>
-        </is>
-      </c>
-    </row>
+          <t>危險時便會用毒針攻擊。</t>
+        </is>
+      </c>
+    </row>
+    <row r="316"/>
     <row r="317">
       <c r="B317" t="inlineStr">
         <is>
@@ -4483,6 +4546,7 @@
         </is>
       </c>
     </row>
+    <row r="321"/>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
@@ -4513,7 +4577,7 @@
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>頭上的犄角裡含有毒素，</t>
+          <t>頭上的角裡含有毒素。</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4599,7 @@
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>當犄角撞穿了什麼東西時，</t>
+          <t>當角刺進敵人身上時，</t>
         </is>
       </c>
     </row>
@@ -4557,10 +4621,11 @@
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>毒素就會隨著衝擊而流出。</t>
-        </is>
-      </c>
-    </row>
+          <t>毒素就會隨衝擊流出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="326"/>
     <row r="327">
       <c r="B327" t="inlineStr">
         <is>
@@ -4609,6 +4674,7 @@
         </is>
       </c>
     </row>
+    <row r="331"/>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
@@ -4639,7 +4705,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>透過活用自己鋼一般堅硬的</t>
+          <t>活用鋼一般堅硬的皮膚，</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4727,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>皮膚來使出強力的撞擊。</t>
+          <t>使出強力的撞擊。</t>
         </is>
       </c>
     </row>
@@ -4683,10 +4749,11 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>犄角堅硬得能夠刺穿鑽石。</t>
-        </is>
-      </c>
-    </row>
+          <t>角堅硬得能夠刺穿鑽石。</t>
+        </is>
+      </c>
+    </row>
+    <row r="336"/>
     <row r="337">
       <c r="B337" t="inlineStr">
         <is>
@@ -4735,6 +4802,7 @@
         </is>
       </c>
     </row>
+    <row r="341"/>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
@@ -4813,6 +4881,7 @@
         </is>
       </c>
     </row>
+    <row r="346"/>
     <row r="347">
       <c r="B347" t="inlineStr">
         <is>
@@ -4861,6 +4930,7 @@
         </is>
       </c>
     </row>
+    <row r="351"/>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
@@ -4939,6 +5009,7 @@
         </is>
       </c>
     </row>
+    <row r="356"/>
     <row r="357">
       <c r="B357" t="inlineStr">
         <is>
@@ -4987,6 +5058,7 @@
         </is>
       </c>
     </row>
+    <row r="361"/>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
@@ -5065,6 +5137,7 @@
         </is>
       </c>
     </row>
+    <row r="366"/>
     <row r="367">
       <c r="B367" t="inlineStr">
         <is>
@@ -5113,6 +5186,7 @@
         </is>
       </c>
     </row>
+    <row r="371"/>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
@@ -5165,7 +5239,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>是由９位聖者</t>
+          <t>是由９位高貴的聖者</t>
         </is>
       </c>
     </row>
@@ -5187,10 +5261,11 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>合體之後而誕生的。</t>
-        </is>
-      </c>
-    </row>
+          <t>合而為一後誕生的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="376"/>
     <row r="377">
       <c r="B377" t="inlineStr">
         <is>
@@ -5239,6 +5314,7 @@
         </is>
       </c>
     </row>
+    <row r="381"/>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
@@ -5269,7 +5345,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>它會用圓溜溜的大眼睛盯著</t>
+          <t>會用圓溜溜的大眼睛</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5367,7 @@
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>對手唱起不可思議的歌曲，</t>
+          <t>凝視對手，再唱起悅耳的</t>
         </is>
       </c>
     </row>
@@ -5313,10 +5389,11 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>舒服的歌曲會讓對手睡著。</t>
-        </is>
-      </c>
-    </row>
+          <t>歌聲讓對手睡著。</t>
+        </is>
+      </c>
+    </row>
+    <row r="386"/>
     <row r="387">
       <c r="B387" t="inlineStr">
         <is>
@@ -5365,6 +5442,7 @@
         </is>
       </c>
     </row>
+    <row r="391"/>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
@@ -5443,6 +5521,7 @@
         </is>
       </c>
     </row>
+    <row r="396"/>
     <row r="397">
       <c r="B397" t="inlineStr">
         <is>
@@ -5491,6 +5570,7 @@
         </is>
       </c>
     </row>
+    <row r="401"/>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
@@ -5521,7 +5601,7 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>由於需要調查前方的狀況，</t>
+          <t>飛行時會從嘴裡發出</t>
         </is>
       </c>
     </row>
@@ -5543,7 +5623,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>它會一邊從嘴裡發出超音波</t>
+          <t>超音波，像聲納一樣</t>
         </is>
       </c>
     </row>
@@ -5565,10 +5645,11 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>一邊飛行。</t>
-        </is>
-      </c>
-    </row>
+          <t>確認前方有沒有障礙物。</t>
+        </is>
+      </c>
+    </row>
+    <row r="406"/>
     <row r="407">
       <c r="B407" t="inlineStr">
         <is>
@@ -5617,6 +5698,7 @@
         </is>
       </c>
     </row>
+    <row r="411"/>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
@@ -5695,6 +5777,7 @@
         </is>
       </c>
     </row>
+    <row r="416"/>
     <row r="417">
       <c r="B417" t="inlineStr">
         <is>
@@ -5743,6 +5826,7 @@
         </is>
       </c>
     </row>
+    <row r="421"/>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
@@ -5817,10 +5901,11 @@
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>這讓人感到莫名的恐怖。</t>
-        </is>
-      </c>
-    </row>
+          <t>令人感到莫名恐怖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="426"/>
     <row r="427">
       <c r="B427" t="inlineStr">
         <is>
@@ -5869,6 +5954,7 @@
         </is>
       </c>
     </row>
+    <row r="431"/>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
@@ -5921,7 +6007,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>一千個人裡總會出現</t>
+          <t>約每１０００人之中</t>
         </is>
       </c>
     </row>
@@ -5943,10 +6029,11 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>一個人喜歡聞這種味道。</t>
-        </is>
-      </c>
-    </row>
+          <t>就有１人喜歡聞這種味道。</t>
+        </is>
+      </c>
+    </row>
+    <row r="436"/>
     <row r="437">
       <c r="B437" t="inlineStr">
         <is>
@@ -5995,6 +6082,7 @@
         </is>
       </c>
     </row>
+    <row r="441"/>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
@@ -6073,6 +6161,7 @@
         </is>
       </c>
     </row>
+    <row r="446"/>
     <row r="447">
       <c r="B447" t="inlineStr">
         <is>
@@ -6121,6 +6210,7 @@
         </is>
       </c>
     </row>
+    <row r="451"/>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
@@ -6199,6 +6289,7 @@
         </is>
       </c>
     </row>
+    <row r="456"/>
     <row r="457">
       <c r="B457" t="inlineStr">
         <is>
@@ -6247,6 +6338,7 @@
         </is>
       </c>
     </row>
+    <row r="461"/>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
@@ -6277,7 +6369,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>因蟲子的精華不斷被吸走，</t>
+          <t>寄主的精力被背上的蘑菇</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6391,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>在思考的似乎已經不是</t>
+          <t>不斷吸收。似乎負責思考的</t>
         </is>
       </c>
     </row>
@@ -6321,10 +6413,11 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>蟲子，而是背上的蘑菇了。</t>
-        </is>
-      </c>
-    </row>
+          <t>已經是蘑菇了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="466"/>
     <row r="467">
       <c r="B467" t="inlineStr">
         <is>
@@ -6373,6 +6466,7 @@
         </is>
       </c>
     </row>
+    <row r="471"/>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
@@ -6403,7 +6497,7 @@
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>在明亮處你便能發現它具有</t>
+          <t>在明亮處便能發現，</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6519,7 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>雷達功能的大眼其實是由</t>
+          <t>具有雷達功能的大眼睛</t>
         </is>
       </c>
     </row>
@@ -6447,10 +6541,11 @@
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>許多個小眼睛聚集而成的。</t>
-        </is>
-      </c>
-    </row>
+          <t>其實是許多小眼睛聚成的。</t>
+        </is>
+      </c>
+    </row>
+    <row r="476"/>
     <row r="477">
       <c r="B477" t="inlineStr">
         <is>
@@ -6499,6 +6594,7 @@
         </is>
       </c>
     </row>
+    <row r="481"/>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
@@ -6529,7 +6625,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>若失手把翅膀上的鱗粉沾到</t>
+          <t>翅膀上的鱗粉一旦沾到</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6647,7 @@
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>身上，不但很難去除，更糟</t>
+          <t>身上，不但很難去除，</t>
         </is>
       </c>
     </row>
@@ -6573,10 +6669,11 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>的是毒素也會從那裡滲入。</t>
-        </is>
-      </c>
-    </row>
+          <t>毒素也會從那裡滲入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="486"/>
     <row r="487">
       <c r="B487" t="inlineStr">
         <is>
@@ -6625,6 +6722,7 @@
         </is>
       </c>
     </row>
+    <row r="491"/>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
@@ -6699,10 +6797,11 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>只在洞窟裡會常探頭出來。</t>
-        </is>
-      </c>
-    </row>
+          <t>有時會在洞窟裡探頭出來。</t>
+        </is>
+      </c>
+    </row>
+    <row r="496"/>
     <row r="497">
       <c r="B497" t="inlineStr">
         <is>
@@ -6751,6 +6850,7 @@
         </is>
       </c>
     </row>
+    <row r="501"/>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
@@ -6781,7 +6881,7 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>三合一的力量能讓它們</t>
+          <t>由三胞胎組成。挖洞速度</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6903,7 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>挖地深至１００公里，甚至</t>
+          <t>可超過時速１００公里，</t>
         </is>
       </c>
     </row>
@@ -6825,10 +6925,11 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>有報告說它們會引發地震。</t>
-        </is>
-      </c>
-    </row>
+          <t>有人會誤以為是地震。</t>
+        </is>
+      </c>
+    </row>
+    <row r="506"/>
     <row r="507">
       <c r="B507" t="inlineStr">
         <is>
@@ -6877,6 +6978,7 @@
         </is>
       </c>
     </row>
+    <row r="511"/>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
@@ -6907,7 +7009,7 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>貌似一到晚上就精力充沛。</t>
+          <t>似乎一到晚上就精力充沛。</t>
         </is>
       </c>
     </row>
@@ -6955,6 +7057,7 @@
         </is>
       </c>
     </row>
+    <row r="516"/>
     <row r="517">
       <c r="B517" t="inlineStr">
         <is>
@@ -7003,6 +7106,7 @@
         </is>
       </c>
     </row>
+    <row r="521"/>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
@@ -7081,6 +7185,7 @@
         </is>
       </c>
     </row>
+    <row r="526"/>
     <row r="527">
       <c r="B527" t="inlineStr">
         <is>
@@ -7129,6 +7234,7 @@
         </is>
       </c>
     </row>
+    <row r="531"/>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
@@ -7207,6 +7313,7 @@
         </is>
       </c>
     </row>
+    <row r="536"/>
     <row r="537">
       <c r="B537" t="inlineStr">
         <is>
@@ -7255,6 +7362,7 @@
         </is>
       </c>
     </row>
+    <row r="541"/>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
@@ -7333,6 +7441,7 @@
         </is>
       </c>
     </row>
+    <row r="546"/>
     <row r="547">
       <c r="B547" t="inlineStr">
         <is>
@@ -7381,6 +7490,7 @@
         </is>
       </c>
     </row>
+    <row r="551"/>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
@@ -7433,7 +7543,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>常因雞毛蒜皮的小事發火</t>
+          <t>很容易因一點小事發火，</t>
         </is>
       </c>
     </row>
@@ -7455,10 +7565,11 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>而飛撲到周圍的東西上。</t>
-        </is>
-      </c>
-    </row>
+          <t>毫不猶豫地攻擊周遭事物。</t>
+        </is>
+      </c>
+    </row>
+    <row r="556"/>
     <row r="557">
       <c r="B557" t="inlineStr">
         <is>
@@ -7507,6 +7618,7 @@
         </is>
       </c>
     </row>
+    <row r="561"/>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
@@ -7585,6 +7697,7 @@
         </is>
       </c>
     </row>
+    <row r="566"/>
     <row r="567">
       <c r="B567" t="inlineStr">
         <is>
@@ -7633,6 +7746,7 @@
         </is>
       </c>
     </row>
+    <row r="571"/>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
@@ -7711,6 +7825,7 @@
         </is>
       </c>
     </row>
+    <row r="576"/>
     <row r="577">
       <c r="B577" t="inlineStr">
         <is>
@@ -7759,6 +7874,7 @@
         </is>
       </c>
     </row>
+    <row r="581"/>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
@@ -7833,10 +7949,11 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>輕巧跑動的身姿而傾倒。</t>
-        </is>
-      </c>
-    </row>
+          <t>奔跑時的優雅身姿而傾倒。</t>
+        </is>
+      </c>
+    </row>
+    <row r="586"/>
     <row r="587">
       <c r="B587" t="inlineStr">
         <is>
@@ -7885,6 +8002,7 @@
         </is>
       </c>
     </row>
+    <row r="591"/>
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
@@ -7963,6 +8081,7 @@
         </is>
       </c>
     </row>
+    <row r="596"/>
     <row r="597">
       <c r="B597" t="inlineStr">
         <is>
@@ -8011,6 +8130,7 @@
         </is>
       </c>
     </row>
+    <row r="601"/>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
@@ -8089,6 +8209,7 @@
         </is>
       </c>
     </row>
+    <row r="606"/>
     <row r="607">
       <c r="B607" t="inlineStr">
         <is>
@@ -8137,6 +8258,7 @@
         </is>
       </c>
     </row>
+    <row r="611"/>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
@@ -8167,7 +8289,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>他會用全身的肌肉奮力</t>
+          <t>它會用全身的肌肉奮力</t>
         </is>
       </c>
     </row>
@@ -8215,6 +8337,7 @@
         </is>
       </c>
     </row>
+    <row r="616"/>
     <row r="617">
       <c r="B617" t="inlineStr">
         <is>
@@ -8263,6 +8386,7 @@
         </is>
       </c>
     </row>
+    <row r="621"/>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
@@ -8341,6 +8465,7 @@
         </is>
       </c>
     </row>
+    <row r="626"/>
     <row r="627">
       <c r="B627" t="inlineStr">
         <is>
@@ -8389,6 +8514,7 @@
         </is>
       </c>
     </row>
+    <row r="631"/>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
@@ -8467,6 +8593,7 @@
         </is>
       </c>
     </row>
+    <row r="636"/>
     <row r="637">
       <c r="B637" t="inlineStr">
         <is>
@@ -8515,6 +8642,7 @@
         </is>
       </c>
     </row>
+    <row r="641"/>
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
@@ -8593,6 +8721,7 @@
         </is>
       </c>
     </row>
+    <row r="646"/>
     <row r="647">
       <c r="B647" t="inlineStr">
         <is>
@@ -8641,6 +8770,7 @@
         </is>
       </c>
     </row>
+    <row r="651"/>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
@@ -8719,6 +8849,7 @@
         </is>
       </c>
     </row>
+    <row r="656"/>
     <row r="657">
       <c r="B657" t="inlineStr">
         <is>
@@ -8767,6 +8898,7 @@
         </is>
       </c>
     </row>
+    <row r="661"/>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
@@ -8797,7 +8929,7 @@
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>只要解開繫在腰上的限制它</t>
+          <t>腰帶限制著力量。</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8951,7 @@
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>力量的腰帶，豪力就會變得</t>
+          <t>一旦解開，豪力就會</t>
         </is>
       </c>
     </row>
@@ -8841,10 +8973,11 @@
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>勢不可擋。</t>
-        </is>
-      </c>
-    </row>
+          <t>變得勢不可擋。</t>
+        </is>
+      </c>
+    </row>
+    <row r="666"/>
     <row r="667">
       <c r="B667" t="inlineStr">
         <is>
@@ -8893,6 +9026,7 @@
         </is>
       </c>
     </row>
+    <row r="671"/>
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
@@ -8971,6 +9105,7 @@
         </is>
       </c>
     </row>
+    <row r="676"/>
     <row r="677">
       <c r="B677" t="inlineStr">
         <is>
@@ -9019,6 +9154,7 @@
         </is>
       </c>
     </row>
+    <row r="681"/>
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
@@ -9049,7 +9185,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>喜歡溫度高，有一定溼度的</t>
+          <t>喜歡高溫潮濕的地方。</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9207,7 @@
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>地方。它會用身上的藤蔓</t>
+          <t>它會用身上的藤蔓</t>
         </is>
       </c>
     </row>
@@ -9097,6 +9233,7 @@
         </is>
       </c>
     </row>
+    <row r="686"/>
     <row r="687">
       <c r="B687" t="inlineStr">
         <is>
@@ -9145,6 +9282,7 @@
         </is>
       </c>
     </row>
+    <row r="691"/>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
@@ -9175,7 +9313,7 @@
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>它在肚子餓的時候會吞掉</t>
+          <t>肚子餓時會吞掉</t>
         </is>
       </c>
     </row>
@@ -9219,10 +9357,11 @@
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>分泌溶解液讓其致命。</t>
-        </is>
-      </c>
-    </row>
+          <t>並用強酸將獵物溶解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="696"/>
     <row r="697">
       <c r="B697" t="inlineStr">
         <is>
@@ -9271,6 +9410,7 @@
         </is>
       </c>
     </row>
+    <row r="701"/>
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
@@ -9301,7 +9441,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>用花蜜香味引誘獵物。據說</t>
+          <t>用花蜜香味引誘獵物。</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9463,7 @@
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>被它吞入嘴裡的東西，只要</t>
+          <t>據說被它整個吞下後，</t>
         </is>
       </c>
     </row>
@@ -9345,10 +9485,11 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>１天會溶解到骨頭都不剩。</t>
-        </is>
-      </c>
-    </row>
+          <t>１天內就會溶到骨頭不剩。</t>
+        </is>
+      </c>
+    </row>
+    <row r="706"/>
     <row r="707">
       <c r="B707" t="inlineStr">
         <is>
@@ -9397,6 +9538,7 @@
         </is>
       </c>
     </row>
+    <row r="711"/>
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
@@ -9449,7 +9591,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>乾巴巴的身體，但是</t>
+          <t>乾巴巴的身體。只要把它</t>
         </is>
       </c>
     </row>
@@ -9471,10 +9613,11 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>它只要沾到水就能復活。</t>
-        </is>
-      </c>
-    </row>
+          <t>放回海裡就能復活。</t>
+        </is>
+      </c>
+    </row>
+    <row r="716"/>
     <row r="717">
       <c r="B717" t="inlineStr">
         <is>
@@ -9523,6 +9666,7 @@
         </is>
       </c>
     </row>
+    <row r="721"/>
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
@@ -9601,6 +9745,7 @@
         </is>
       </c>
     </row>
+    <row r="726"/>
     <row r="727">
       <c r="B727" t="inlineStr">
         <is>
@@ -9649,6 +9794,7 @@
         </is>
       </c>
     </row>
+    <row r="731"/>
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
@@ -9679,7 +9825,7 @@
       </c>
       <c r="G733" t="inlineStr">
         <is>
-          <t>大多棲息於山路。由於</t>
+          <t>常見於山路等地方。</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9847,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>不留神踩到它會使它</t>
+          <t>如果不小心踩到它，</t>
         </is>
       </c>
     </row>
@@ -9723,10 +9869,11 @@
       </c>
       <c r="G735" t="inlineStr">
         <is>
-          <t>大發雷霆，得多加小心。</t>
-        </is>
-      </c>
-    </row>
+          <t>它就會大發雷霆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="736"/>
     <row r="737">
       <c r="B737" t="inlineStr">
         <is>
@@ -9775,6 +9922,7 @@
         </is>
       </c>
     </row>
+    <row r="741"/>
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
@@ -9827,7 +9975,7 @@
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>滾動時從來不關心</t>
+          <t>滾動時完全不在乎</t>
         </is>
       </c>
     </row>
@@ -9849,10 +9997,11 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>前面的路上都有什麼。</t>
-        </is>
-      </c>
-    </row>
+          <t>前方有什麼障礙。</t>
+        </is>
+      </c>
+    </row>
+    <row r="746"/>
     <row r="747">
       <c r="B747" t="inlineStr">
         <is>
@@ -9901,6 +10050,7 @@
         </is>
       </c>
     </row>
+    <row r="751"/>
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
@@ -9979,6 +10129,7 @@
         </is>
       </c>
     </row>
+    <row r="756"/>
     <row r="757">
       <c r="B757" t="inlineStr">
         <is>
@@ -10027,6 +10178,7 @@
         </is>
       </c>
     </row>
+    <row r="761"/>
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
@@ -10105,6 +10257,7 @@
         </is>
       </c>
     </row>
+    <row r="766"/>
     <row r="767">
       <c r="B767" t="inlineStr">
         <is>
@@ -10153,6 +10306,7 @@
         </is>
       </c>
     </row>
+    <row r="771"/>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
@@ -10231,6 +10385,7 @@
         </is>
       </c>
     </row>
+    <row r="776"/>
     <row r="777">
       <c r="B777" t="inlineStr">
         <is>
@@ -10279,6 +10434,7 @@
         </is>
       </c>
     </row>
+    <row r="781"/>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
@@ -10309,7 +10465,7 @@
       </c>
       <c r="G783" t="inlineStr">
         <is>
-          <t>非常呆，動作也很緩慢。</t>
+          <t>非常遲鈍，動作也很緩慢。</t>
         </is>
       </c>
     </row>
@@ -10357,6 +10513,7 @@
         </is>
       </c>
     </row>
+    <row r="786"/>
     <row r="787">
       <c r="B787" t="inlineStr">
         <is>
@@ -10405,6 +10562,7 @@
         </is>
       </c>
     </row>
+    <row r="791"/>
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
@@ -10483,6 +10641,7 @@
         </is>
       </c>
     </row>
+    <row r="796"/>
     <row r="797">
       <c r="B797" t="inlineStr">
         <is>
@@ -10531,6 +10690,7 @@
         </is>
       </c>
     </row>
+    <row r="801"/>
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
@@ -10561,7 +10721,7 @@
       </c>
       <c r="G803" t="inlineStr">
         <is>
-          <t>天生就擁有遮斷重力的</t>
+          <t>天生就擁有抵抗重力的</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10743,7 @@
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>能力，可以一邊發出</t>
+          <t>能力，會靠強力電磁波</t>
         </is>
       </c>
     </row>
@@ -10605,10 +10765,11 @@
       </c>
       <c r="G805" t="inlineStr">
         <is>
-          <t>電磁波一邊在空中移動。</t>
-        </is>
-      </c>
-    </row>
+          <t>漂浮在空中。</t>
+        </is>
+      </c>
+    </row>
+    <row r="806"/>
     <row r="807">
       <c r="B807" t="inlineStr">
         <is>
@@ -10657,6 +10818,7 @@
         </is>
       </c>
     </row>
+    <row r="811"/>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
@@ -10735,6 +10897,7 @@
         </is>
       </c>
     </row>
+    <row r="816"/>
     <row r="817">
       <c r="B817" t="inlineStr">
         <is>
@@ -10783,6 +10946,7 @@
         </is>
       </c>
     </row>
+    <row r="821"/>
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
@@ -10861,6 +11025,7 @@
         </is>
       </c>
     </row>
+    <row r="826"/>
     <row r="827">
       <c r="B827" t="inlineStr">
         <is>
@@ -10909,6 +11074,7 @@
         </is>
       </c>
     </row>
+    <row r="831"/>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
@@ -10987,6 +11153,7 @@
         </is>
       </c>
     </row>
+    <row r="836"/>
     <row r="837">
       <c r="B837" t="inlineStr">
         <is>
@@ -11035,6 +11202,7 @@
         </is>
       </c>
     </row>
+    <row r="841"/>
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
@@ -11087,7 +11255,7 @@
       </c>
       <c r="G844" t="inlineStr">
         <is>
-          <t>變種。以６０千米的時速</t>
+          <t>變種。以時速６０公里</t>
         </is>
       </c>
     </row>
@@ -11113,6 +11281,7 @@
         </is>
       </c>
     </row>
+    <row r="846"/>
     <row r="847">
       <c r="B847" t="inlineStr">
         <is>
@@ -11161,6 +11330,7 @@
         </is>
       </c>
     </row>
+    <row r="851"/>
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
@@ -11239,6 +11409,7 @@
         </is>
       </c>
     </row>
+    <row r="856"/>
     <row r="857">
       <c r="B857" t="inlineStr">
         <is>
@@ -11287,6 +11458,7 @@
         </is>
       </c>
     </row>
+    <row r="861"/>
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
@@ -11365,6 +11537,7 @@
         </is>
       </c>
     </row>
+    <row r="866"/>
     <row r="867">
       <c r="B867" t="inlineStr">
         <is>
@@ -11413,6 +11586,7 @@
         </is>
       </c>
     </row>
+    <row r="871"/>
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
@@ -11443,7 +11617,7 @@
       </c>
       <c r="G873" t="inlineStr">
         <is>
-          <t>它由囤積的淤泥而形成。</t>
+          <t>它是由凝固的淤泥形成。</t>
         </is>
       </c>
     </row>
@@ -11491,6 +11665,7 @@
         </is>
       </c>
     </row>
+    <row r="876"/>
     <row r="877">
       <c r="B877" t="inlineStr">
         <is>
@@ -11539,6 +11714,7 @@
         </is>
       </c>
     </row>
+    <row r="881"/>
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
@@ -11591,7 +11767,7 @@
       </c>
       <c r="G884" t="inlineStr">
         <is>
-          <t>窒息，但由於鼻子的退化，</t>
+          <t>昏倒，但由於鼻子退化，</t>
         </is>
       </c>
     </row>
@@ -11617,6 +11793,7 @@
         </is>
       </c>
     </row>
+    <row r="886"/>
     <row r="887">
       <c r="B887" t="inlineStr">
         <is>
@@ -11665,6 +11842,7 @@
         </is>
       </c>
     </row>
+    <row r="891"/>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
@@ -11717,7 +11895,7 @@
       </c>
       <c r="G894" t="inlineStr">
         <is>
-          <t>攻擊，但是一旦硬殼開啟，</t>
+          <t>攻擊，但是一旦硬殼張開，</t>
         </is>
       </c>
     </row>
@@ -11743,6 +11921,7 @@
         </is>
       </c>
     </row>
+    <row r="896"/>
     <row r="897">
       <c r="B897" t="inlineStr">
         <is>
@@ -11791,6 +11970,7 @@
         </is>
       </c>
     </row>
+    <row r="901"/>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
@@ -11869,6 +12049,7 @@
         </is>
       </c>
     </row>
+    <row r="906"/>
     <row r="907">
       <c r="B907" t="inlineStr">
         <is>
@@ -11917,6 +12098,7 @@
         </is>
       </c>
     </row>
+    <row r="911"/>
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
@@ -11995,6 +12177,7 @@
         </is>
       </c>
     </row>
+    <row r="916"/>
     <row r="917">
       <c r="B917" t="inlineStr">
         <is>
@@ -12043,6 +12226,7 @@
         </is>
       </c>
     </row>
+    <row r="921"/>
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
@@ -12117,10 +12301,11 @@
       </c>
       <c r="G925" t="inlineStr">
         <is>
-          <t>不停顫抖，最後一命嗚呼。</t>
-        </is>
-      </c>
-    </row>
+          <t>顫抖，最後失去生命。</t>
+        </is>
+      </c>
+    </row>
+    <row r="926"/>
     <row r="927">
       <c r="B927" t="inlineStr">
         <is>
@@ -12169,6 +12354,7 @@
         </is>
       </c>
     </row>
+    <row r="931"/>
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
@@ -12247,6 +12433,7 @@
         </is>
       </c>
     </row>
+    <row r="936"/>
     <row r="937">
       <c r="B937" t="inlineStr">
         <is>
@@ -12295,6 +12482,7 @@
         </is>
       </c>
     </row>
+    <row r="941"/>
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
@@ -12325,7 +12513,7 @@
       </c>
       <c r="G943" t="inlineStr">
         <is>
-          <t>以驚人之勢鑽地覓食。在它</t>
+          <t>高速鑽地尋找食物。</t>
         </is>
       </c>
     </row>
@@ -12347,7 +12535,7 @@
       </c>
       <c r="G944" t="inlineStr">
         <is>
-          <t>通過之後形成的洞穴會被</t>
+          <t>它留下的隧道會被</t>
         </is>
       </c>
     </row>
@@ -12369,10 +12557,11 @@
       </c>
       <c r="G945" t="inlineStr">
         <is>
-          <t>地鼠們當作自己的住處。</t>
-        </is>
-      </c>
-    </row>
+          <t>地鼠們當作住處。</t>
+        </is>
+      </c>
+    </row>
+    <row r="946"/>
     <row r="947">
       <c r="B947" t="inlineStr">
         <is>
@@ -12421,6 +12610,7 @@
         </is>
       </c>
     </row>
+    <row r="951"/>
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
@@ -12499,6 +12689,7 @@
         </is>
       </c>
     </row>
+    <row r="956"/>
     <row r="957">
       <c r="B957" t="inlineStr">
         <is>
@@ -12547,6 +12738,7 @@
         </is>
       </c>
     </row>
+    <row r="961"/>
     <row r="962">
       <c r="A962" t="inlineStr">
         <is>
@@ -12577,7 +12769,7 @@
       </c>
       <c r="G963" t="inlineStr">
         <is>
-          <t>無意中遇到它的時候，若意</t>
+          <t>無意中遇到它時，</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12791,7 @@
       </c>
       <c r="G964" t="inlineStr">
         <is>
-          <t>外和他對上視線會很危險。</t>
+          <t>別和它對上眼。</t>
         </is>
       </c>
     </row>
@@ -12621,10 +12813,11 @@
       </c>
       <c r="G965" t="inlineStr">
         <is>
-          <t>它手上的鐘擺會讓人睡著。</t>
-        </is>
-      </c>
-    </row>
+          <t>它會用鐘擺催眠你。</t>
+        </is>
+      </c>
+    </row>
+    <row r="966"/>
     <row r="967">
       <c r="B967" t="inlineStr">
         <is>
@@ -12673,6 +12866,7 @@
         </is>
       </c>
     </row>
+    <row r="971"/>
     <row r="972">
       <c r="A972" t="inlineStr">
         <is>
@@ -12751,6 +12945,7 @@
         </is>
       </c>
     </row>
+    <row r="976"/>
     <row r="977">
       <c r="B977" t="inlineStr">
         <is>
@@ -12799,6 +12994,7 @@
         </is>
       </c>
     </row>
+    <row r="981"/>
     <row r="982">
       <c r="A982" t="inlineStr">
         <is>
@@ -12829,7 +13025,7 @@
       </c>
       <c r="G983" t="inlineStr">
         <is>
-          <t>一邊的鉗子很是巨大，雖說</t>
+          <t>一邊的鉗子巨大無比，</t>
         </is>
       </c>
     </row>
@@ -12851,7 +13047,7 @@
       </c>
       <c r="G984" t="inlineStr">
         <is>
-          <t>硬如鋼鐵還擁有１萬馬力，</t>
+          <t>硬如鋼鐵且有１萬馬力，</t>
         </is>
       </c>
     </row>
@@ -12873,10 +13069,11 @@
       </c>
       <c r="G985" t="inlineStr">
         <is>
-          <t>但還是太重了。</t>
-        </is>
-      </c>
-    </row>
+          <t>但實在太重了。</t>
+        </is>
+      </c>
+    </row>
+    <row r="986"/>
     <row r="987">
       <c r="B987" t="inlineStr">
         <is>
@@ -12925,6 +13122,7 @@
         </is>
       </c>
     </row>
+    <row r="991"/>
     <row r="992">
       <c r="A992" t="inlineStr">
         <is>
@@ -12977,7 +13175,7 @@
       </c>
       <c r="G994" t="inlineStr">
         <is>
-          <t>其實是保護色，但它很容易</t>
+          <t>其實是保護色，受到一點</t>
         </is>
       </c>
     </row>
@@ -12999,10 +13197,11 @@
       </c>
       <c r="G995" t="inlineStr">
         <is>
-          <t>自爆這一點也出人意料。</t>
-        </is>
-      </c>
-    </row>
+          <t>刺激就會自爆。</t>
+        </is>
+      </c>
+    </row>
+    <row r="996"/>
     <row r="997">
       <c r="B997" t="inlineStr">
         <is>
@@ -13051,6 +13250,7 @@
         </is>
       </c>
     </row>
+    <row r="1001"/>
     <row r="1002">
       <c r="A1002" t="inlineStr">
         <is>
@@ -13103,7 +13303,7 @@
       </c>
       <c r="G1004" t="inlineStr">
         <is>
-          <t>就會由於體內的電能溢位</t>
+          <t>就會因為體內電能溢出，</t>
         </is>
       </c>
     </row>
@@ -13125,10 +13325,11 @@
       </c>
       <c r="G1005" t="inlineStr">
         <is>
-          <t>導致爆炸。</t>
-        </is>
-      </c>
-    </row>
+          <t>導致大爆炸。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006"/>
     <row r="1007">
       <c r="B1007" t="inlineStr">
         <is>
@@ -13177,6 +13378,7 @@
         </is>
       </c>
     </row>
+    <row r="1011"/>
     <row r="1012">
       <c r="A1012" t="inlineStr">
         <is>
@@ -13255,6 +13457,7 @@
         </is>
       </c>
     </row>
+    <row r="1016"/>
     <row r="1017">
       <c r="B1017" t="inlineStr">
         <is>
@@ -13303,6 +13506,7 @@
         </is>
       </c>
     </row>
+    <row r="1021"/>
     <row r="1022">
       <c r="A1022" t="inlineStr">
         <is>
@@ -13381,6 +13585,7 @@
         </is>
       </c>
     </row>
+    <row r="1026"/>
     <row r="1027">
       <c r="B1027" t="inlineStr">
         <is>
@@ -13429,6 +13634,7 @@
         </is>
       </c>
     </row>
+    <row r="1031"/>
     <row r="1032">
       <c r="A1032" t="inlineStr">
         <is>
@@ -13507,6 +13713,7 @@
         </is>
       </c>
     </row>
+    <row r="1036"/>
     <row r="1037">
       <c r="B1037" t="inlineStr">
         <is>
@@ -13555,6 +13762,7 @@
         </is>
       </c>
     </row>
+    <row r="1041"/>
     <row r="1042">
       <c r="A1042" t="inlineStr">
         <is>
@@ -13633,6 +13841,7 @@
         </is>
       </c>
     </row>
+    <row r="1046"/>
     <row r="1047">
       <c r="B1047" t="inlineStr">
         <is>
@@ -13681,6 +13890,7 @@
         </is>
       </c>
     </row>
+    <row r="1051"/>
     <row r="1052">
       <c r="A1052" t="inlineStr">
         <is>
@@ -13755,10 +13965,11 @@
       </c>
       <c r="G1055" t="inlineStr">
         <is>
-          <t>將對手踢成碎片。</t>
-        </is>
-      </c>
-    </row>
+          <t>能將對手踢碎。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056"/>
     <row r="1057">
       <c r="B1057" t="inlineStr">
         <is>
@@ -13807,6 +14018,7 @@
         </is>
       </c>
     </row>
+    <row r="1061"/>
     <row r="1062">
       <c r="A1062" t="inlineStr">
         <is>
@@ -13885,6 +14097,7 @@
         </is>
       </c>
     </row>
+    <row r="1066"/>
     <row r="1067">
       <c r="B1067" t="inlineStr">
         <is>
@@ -13933,6 +14146,7 @@
         </is>
       </c>
     </row>
+    <row r="1071"/>
     <row r="1072">
       <c r="A1072" t="inlineStr">
         <is>
@@ -13963,7 +14177,7 @@
       </c>
       <c r="G1073" t="inlineStr">
         <is>
-          <t>它２米長的舌頭比前肢更能</t>
+          <t>近２公尺長的舌頭</t>
         </is>
       </c>
     </row>
@@ -13985,7 +14199,7 @@
       </c>
       <c r="G1074" t="inlineStr">
         <is>
-          <t>靈活地移動。不知為何，</t>
+          <t>比前肢更靈活。不知為何，</t>
         </is>
       </c>
     </row>
@@ -14007,10 +14221,11 @@
       </c>
       <c r="G1075" t="inlineStr">
         <is>
-          <t>被它舔到之後會覺得發麻。</t>
-        </is>
-      </c>
-    </row>
+          <t>被它舔到後會覺得發麻。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076"/>
     <row r="1077">
       <c r="B1077" t="inlineStr">
         <is>
@@ -14059,6 +14274,7 @@
         </is>
       </c>
     </row>
+    <row r="1081"/>
     <row r="1082">
       <c r="A1082" t="inlineStr">
         <is>
@@ -14111,7 +14327,7 @@
       </c>
       <c r="G1084" t="inlineStr">
         <is>
-          <t>氣體會由於膨脹而產生</t>
+          <t>氣體可能膨脹並突然爆炸。</t>
         </is>
       </c>
     </row>
@@ -14133,10 +14349,11 @@
       </c>
       <c r="G1085" t="inlineStr">
         <is>
-          <t>爆炸的危險，需要注意。</t>
-        </is>
-      </c>
-    </row>
+          <t>務必小心！</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086"/>
     <row r="1087">
       <c r="B1087" t="inlineStr">
         <is>
@@ -14178,6 +14395,7 @@
         </is>
       </c>
     </row>
+    <row r="1090"/>
     <row r="1091">
       <c r="A1091" t="inlineStr">
         <is>
@@ -14256,6 +14474,7 @@
         </is>
       </c>
     </row>
+    <row r="1095"/>
     <row r="1096">
       <c r="B1096" t="inlineStr">
         <is>
@@ -14304,6 +14523,7 @@
         </is>
       </c>
     </row>
+    <row r="1100"/>
     <row r="1101">
       <c r="A1101" t="inlineStr">
         <is>
@@ -14334,7 +14554,7 @@
       </c>
       <c r="G1102" t="inlineStr">
         <is>
-          <t>單細胞的腦子只能思考一件</t>
+          <t>腦袋一根筋，</t>
         </is>
       </c>
     </row>
@@ -14356,7 +14576,7 @@
       </c>
       <c r="G1103" t="inlineStr">
         <is>
-          <t>事情。一旦它開始猛撞，</t>
+          <t>開始猛撞後，</t>
         </is>
       </c>
     </row>
@@ -14378,10 +14598,11 @@
       </c>
       <c r="G1104" t="inlineStr">
         <is>
-          <t>直到睡著前都不會停止。</t>
-        </is>
-      </c>
-    </row>
+          <t>到睡著前都不停。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105"/>
     <row r="1106">
       <c r="B1106" t="inlineStr">
         <is>
@@ -14430,6 +14651,7 @@
         </is>
       </c>
     </row>
+    <row r="1110"/>
     <row r="1111">
       <c r="A1111" t="inlineStr">
         <is>
@@ -14508,6 +14730,7 @@
         </is>
       </c>
     </row>
+    <row r="1115"/>
     <row r="1116">
       <c r="B1116" t="inlineStr">
         <is>
@@ -14556,6 +14779,7 @@
         </is>
       </c>
     </row>
+    <row r="1120"/>
     <row r="1121">
       <c r="A1121" t="inlineStr">
         <is>
@@ -14634,6 +14858,7 @@
         </is>
       </c>
     </row>
+    <row r="1125"/>
     <row r="1126">
       <c r="B1126" t="inlineStr">
         <is>
@@ -14682,6 +14907,7 @@
         </is>
       </c>
     </row>
+    <row r="1130"/>
     <row r="1131">
       <c r="A1131" t="inlineStr">
         <is>
@@ -14760,6 +14986,7 @@
         </is>
       </c>
     </row>
+    <row r="1135"/>
     <row r="1136">
       <c r="B1136" t="inlineStr">
         <is>
@@ -14808,6 +15035,7 @@
         </is>
       </c>
     </row>
+    <row r="1140"/>
     <row r="1141">
       <c r="A1141" t="inlineStr">
         <is>
@@ -14886,6 +15114,7 @@
         </is>
       </c>
     </row>
+    <row r="1145"/>
     <row r="1146">
       <c r="B1146" t="inlineStr">
         <is>
@@ -14934,6 +15163,7 @@
         </is>
       </c>
     </row>
+    <row r="1150"/>
     <row r="1151">
       <c r="A1151" t="inlineStr">
         <is>
@@ -15012,6 +15242,7 @@
         </is>
       </c>
     </row>
+    <row r="1155"/>
     <row r="1156">
       <c r="B1156" t="inlineStr">
         <is>
@@ -15060,6 +15291,7 @@
         </is>
       </c>
     </row>
+    <row r="1160"/>
     <row r="1161">
       <c r="A1161" t="inlineStr">
         <is>
@@ -15138,6 +15370,7 @@
         </is>
       </c>
     </row>
+    <row r="1165"/>
     <row r="1166">
       <c r="B1166" t="inlineStr">
         <is>
@@ -15186,6 +15419,7 @@
         </is>
       </c>
     </row>
+    <row r="1170"/>
     <row r="1171">
       <c r="A1171" t="inlineStr">
         <is>
@@ -15264,6 +15498,7 @@
         </is>
       </c>
     </row>
+    <row r="1175"/>
     <row r="1176">
       <c r="B1176" t="inlineStr">
         <is>
@@ -15312,6 +15547,7 @@
         </is>
       </c>
     </row>
+    <row r="1180"/>
     <row r="1181">
       <c r="A1181" t="inlineStr">
         <is>
@@ -15386,10 +15622,11 @@
       </c>
       <c r="G1184" t="inlineStr">
         <is>
-          <t>打穿河裡的石頭築巢。</t>
-        </is>
-      </c>
-    </row>
+          <t>鑿穿河裡的石頭築巢。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185"/>
     <row r="1186">
       <c r="B1186" t="inlineStr">
         <is>
@@ -15438,6 +15675,7 @@
         </is>
       </c>
     </row>
+    <row r="1190"/>
     <row r="1191">
       <c r="A1191" t="inlineStr">
         <is>
@@ -15516,6 +15754,7 @@
         </is>
       </c>
     </row>
+    <row r="1195"/>
     <row r="1196">
       <c r="B1196" t="inlineStr">
         <is>
@@ -15564,6 +15803,7 @@
         </is>
       </c>
     </row>
+    <row r="1200"/>
     <row r="1201">
       <c r="A1201" t="inlineStr">
         <is>
@@ -15594,7 +15834,7 @@
       </c>
       <c r="G1202" s="1" t="inlineStr">
         <is>
-          <t>據說當被稱為其核心的中心</t>
+          <t>據說當被稱為核心的</t>
         </is>
       </c>
       <c r="J1202" s="1" t="inlineStr">
@@ -15621,7 +15861,7 @@
       </c>
       <c r="G1203" t="inlineStr">
         <is>
-          <t>部分閃爍著七色光芒時，</t>
+          <t>中心部分閃爍七色光芒時，</t>
         </is>
       </c>
       <c r="J1203" t="inlineStr">
@@ -15648,7 +15888,7 @@
       </c>
       <c r="G1204" t="inlineStr">
         <is>
-          <t>就代表著它正在傳達資訊。</t>
+          <t>代表它正在傳達訊息。</t>
         </is>
       </c>
       <c r="I1204" t="inlineStr">
@@ -15662,6 +15902,7 @@
         </is>
       </c>
     </row>
+    <row r="1205"/>
     <row r="1206">
       <c r="B1206" t="inlineStr">
         <is>
@@ -15710,6 +15951,7 @@
         </is>
       </c>
     </row>
+    <row r="1210"/>
     <row r="1211">
       <c r="A1211" t="inlineStr">
         <is>
@@ -15788,6 +16030,7 @@
         </is>
       </c>
     </row>
+    <row r="1215"/>
     <row r="1216">
       <c r="B1216" t="inlineStr">
         <is>
@@ -15836,6 +16079,7 @@
         </is>
       </c>
     </row>
+    <row r="1220"/>
     <row r="1221">
       <c r="A1221" t="inlineStr">
         <is>
@@ -15888,7 +16132,7 @@
       </c>
       <c r="G1223" t="inlineStr">
         <is>
-          <t>用鋒利的鐮刀斬砍的樣子</t>
+          <t>用鋒利鐮刀劈砍的樣子</t>
         </is>
       </c>
     </row>
@@ -15914,6 +16158,7 @@
         </is>
       </c>
     </row>
+    <row r="1225"/>
     <row r="1226">
       <c r="B1226" t="inlineStr">
         <is>
@@ -15962,6 +16207,7 @@
         </is>
       </c>
     </row>
+    <row r="1230"/>
     <row r="1231">
       <c r="A1231" t="inlineStr">
         <is>
@@ -16040,6 +16286,7 @@
         </is>
       </c>
     </row>
+    <row r="1235"/>
     <row r="1236">
       <c r="B1236" t="inlineStr">
         <is>
@@ -16088,6 +16335,7 @@
         </is>
       </c>
     </row>
+    <row r="1240"/>
     <row r="1241">
       <c r="A1241" t="inlineStr">
         <is>
@@ -16118,7 +16366,7 @@
       </c>
       <c r="G1242" t="inlineStr">
         <is>
-          <t>要是發生了大片的停電，</t>
+          <t>要是發生大規模停電，</t>
         </is>
       </c>
     </row>
@@ -16162,10 +16410,11 @@
       </c>
       <c r="G1244" t="inlineStr">
         <is>
-          <t>發電站的電能。</t>
-        </is>
-      </c>
-    </row>
+          <t>發電廠的電能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245"/>
     <row r="1246">
       <c r="B1246" t="inlineStr">
         <is>
@@ -16214,6 +16463,7 @@
         </is>
       </c>
     </row>
+    <row r="1250"/>
     <row r="1251">
       <c r="A1251" t="inlineStr">
         <is>
@@ -16292,6 +16542,7 @@
         </is>
       </c>
     </row>
+    <row r="1255"/>
     <row r="1256">
       <c r="B1256" t="inlineStr">
         <is>
@@ -16340,6 +16591,7 @@
         </is>
       </c>
     </row>
+    <row r="1260"/>
     <row r="1261">
       <c r="A1261" t="inlineStr">
         <is>
@@ -16370,7 +16622,7 @@
       </c>
       <c r="G1262" t="inlineStr">
         <is>
-          <t>用犄角全力夾擊！由於低溫</t>
+          <t>用大角全力夾擊！由於低溫</t>
         </is>
       </c>
     </row>
@@ -16418,6 +16670,7 @@
         </is>
       </c>
     </row>
+    <row r="1265"/>
     <row r="1266">
       <c r="B1266" t="inlineStr">
         <is>
@@ -16466,6 +16719,7 @@
         </is>
       </c>
     </row>
+    <row r="1270"/>
     <row r="1271">
       <c r="A1271" t="inlineStr">
         <is>
@@ -16496,7 +16750,7 @@
       </c>
       <c r="G1272" t="inlineStr">
         <is>
-          <t>精力充沛且個性火暴。一旦</t>
+          <t>精力充沛且個性火爆。</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16772,7 @@
       </c>
       <c r="G1273" t="inlineStr">
         <is>
-          <t>開始奔跑，在撞到東西之前</t>
+          <t>一旦開始奔跑，撞到東西前</t>
         </is>
       </c>
     </row>
@@ -16544,6 +16798,7 @@
         </is>
       </c>
     </row>
+    <row r="1275"/>
     <row r="1276">
       <c r="B1276" t="inlineStr">
         <is>
@@ -16592,6 +16847,7 @@
         </is>
       </c>
     </row>
+    <row r="1280"/>
     <row r="1281">
       <c r="A1281" t="inlineStr">
         <is>
@@ -16622,7 +16878,7 @@
       </c>
       <c r="G1282" t="inlineStr">
         <is>
-          <t>因靠不住而出名的寶可夢。</t>
+          <t>以不可靠聞名。</t>
         </is>
       </c>
     </row>
@@ -16670,6 +16926,7 @@
         </is>
       </c>
     </row>
+    <row r="1285"/>
     <row r="1286">
       <c r="B1286" t="inlineStr">
         <is>
@@ -16718,6 +16975,7 @@
         </is>
       </c>
     </row>
+    <row r="1290"/>
     <row r="1291">
       <c r="A1291" t="inlineStr">
         <is>
@@ -16748,7 +17006,7 @@
       </c>
       <c r="G1292" t="inlineStr">
         <is>
-          <t>性格蠻橫愛破壞。在古代，</t>
+          <t>性格蠻橫，破壞力驚人。</t>
         </is>
       </c>
     </row>
@@ -16770,7 +17028,7 @@
       </c>
       <c r="G1293" t="inlineStr">
         <is>
-          <t>這個恐怖的寶可夢曾有過把</t>
+          <t>在古代，這恐怖的寶可夢</t>
         </is>
       </c>
     </row>
@@ -16792,10 +17050,11 @@
       </c>
       <c r="G1294" t="inlineStr">
         <is>
-          <t>整座城市燒成焦土的記錄。</t>
-        </is>
-      </c>
-    </row>
+          <t>曾有摧毀整座城市的紀錄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295"/>
     <row r="1296">
       <c r="B1296" t="inlineStr">
         <is>
@@ -16844,6 +17103,7 @@
         </is>
       </c>
     </row>
+    <row r="1300"/>
     <row r="1301">
       <c r="A1301" t="inlineStr">
         <is>
@@ -16874,7 +17134,7 @@
       </c>
       <c r="G1302" t="inlineStr">
         <is>
-          <t>它擁有可以理解人類語言的</t>
+          <t>擁有能理解人心的</t>
         </is>
       </c>
     </row>
@@ -16896,7 +17156,7 @@
       </c>
       <c r="G1303" t="inlineStr">
         <is>
-          <t>溫柔之心。會把人載在背上</t>
+          <t>溫柔性情。會把人載在背上</t>
         </is>
       </c>
     </row>
@@ -16922,6 +17182,7 @@
         </is>
       </c>
     </row>
+    <row r="1305"/>
     <row r="1306">
       <c r="B1306" t="inlineStr">
         <is>
@@ -16970,6 +17231,7 @@
         </is>
       </c>
     </row>
+    <row r="1310"/>
     <row r="1311">
       <c r="A1311" t="inlineStr">
         <is>
@@ -17000,7 +17262,7 @@
       </c>
       <c r="G1312" t="inlineStr">
         <is>
-          <t>看到敵人的瞬間身體便如同</t>
+          <t>看到敵人的瞬間，身體就像</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17284,7 @@
       </c>
       <c r="G1313" t="inlineStr">
         <is>
-          <t>要融化一般開始轉變，幾乎</t>
+          <t>融化般開始轉變，幾乎會</t>
         </is>
       </c>
     </row>
@@ -17044,10 +17306,11 @@
       </c>
       <c r="G1314" t="inlineStr">
         <is>
-          <t>變身成和對方相同的樣子。</t>
-        </is>
-      </c>
-    </row>
+          <t>變成和對方相同的樣子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315"/>
     <row r="1316">
       <c r="B1316" t="inlineStr">
         <is>
@@ -17096,6 +17359,7 @@
         </is>
       </c>
     </row>
+    <row r="1320"/>
     <row r="1321">
       <c r="A1321" t="inlineStr">
         <is>
@@ -17170,10 +17434,11 @@
       </c>
       <c r="G1324" t="inlineStr">
         <is>
-          <t>只是生存數量很少。</t>
-        </is>
-      </c>
-    </row>
+          <t>目前存活的個體很少。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325"/>
     <row r="1326">
       <c r="B1326" t="inlineStr">
         <is>
@@ -17222,6 +17487,7 @@
         </is>
       </c>
     </row>
+    <row r="1330"/>
     <row r="1331">
       <c r="A1331" t="inlineStr">
         <is>
@@ -17252,7 +17518,7 @@
       </c>
       <c r="G1332" t="inlineStr">
         <is>
-          <t>它的細胞與水分子相似，</t>
+          <t>細胞結構與水分子相似，</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17540,7 @@
       </c>
       <c r="G1333" t="inlineStr">
         <is>
-          <t>在它溶入於水後，</t>
+          <t>溶入水中後，</t>
         </is>
       </c>
     </row>
@@ -17300,6 +17566,7 @@
         </is>
       </c>
     </row>
+    <row r="1335"/>
     <row r="1336">
       <c r="B1336" t="inlineStr">
         <is>
@@ -17348,6 +17615,7 @@
         </is>
       </c>
     </row>
+    <row r="1340"/>
     <row r="1341">
       <c r="A1341" t="inlineStr">
         <is>
@@ -17400,7 +17668,7 @@
       </c>
       <c r="G1343" t="inlineStr">
         <is>
-          <t>就會大叫或生氣，</t>
+          <t>就容易悲傷或生氣，</t>
         </is>
       </c>
     </row>
@@ -17426,6 +17694,7 @@
         </is>
       </c>
     </row>
+    <row r="1345"/>
     <row r="1346">
       <c r="B1346" t="inlineStr">
         <is>
@@ -17474,6 +17743,7 @@
         </is>
       </c>
     </row>
+    <row r="1350"/>
     <row r="1351">
       <c r="A1351" t="inlineStr">
         <is>
@@ -17552,6 +17822,7 @@
         </is>
       </c>
     </row>
+    <row r="1355"/>
     <row r="1356">
       <c r="B1356" t="inlineStr">
         <is>
@@ -17600,6 +17871,7 @@
         </is>
       </c>
     </row>
+    <row r="1360"/>
     <row r="1361">
       <c r="A1361" t="inlineStr">
         <is>
@@ -17674,10 +17946,11 @@
       </c>
       <c r="G1364" t="inlineStr">
         <is>
-          <t>然而至今也努力未果。</t>
-        </is>
-      </c>
-    </row>
+          <t>但目前還沒有成功案例。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365"/>
     <row r="1366">
       <c r="B1366" t="inlineStr">
         <is>
@@ -17726,6 +17999,7 @@
         </is>
       </c>
     </row>
+    <row r="1370"/>
     <row r="1371">
       <c r="A1371" t="inlineStr">
         <is>
@@ -17778,7 +18052,7 @@
       </c>
       <c r="G1373" t="inlineStr">
         <is>
-          <t>靠巧妙地彎曲它的１０條腿</t>
+          <t>靠巧妙地彎動１０條觸手</t>
         </is>
       </c>
     </row>
@@ -17800,10 +18074,11 @@
       </c>
       <c r="G1374" t="inlineStr">
         <is>
-          <t>在古代的大海裡飄蕩。</t>
-        </is>
-      </c>
-    </row>
+          <t>在古代的大海裡游動。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375"/>
     <row r="1376">
       <c r="B1376" t="inlineStr">
         <is>
@@ -17852,6 +18127,7 @@
         </is>
       </c>
     </row>
+    <row r="1380"/>
     <row r="1381">
       <c r="A1381" t="inlineStr">
         <is>
@@ -17882,7 +18158,7 @@
       </c>
       <c r="G1382" t="inlineStr">
         <is>
-          <t>它擁有鋒利的牙齒，</t>
+          <t>嘴邊長著鋒利的喙。</t>
         </is>
       </c>
     </row>
@@ -17904,7 +18180,7 @@
       </c>
       <c r="G1383" t="inlineStr">
         <is>
-          <t>但據說它由於外殼過大，</t>
+          <t>但據說它因外殼過大，</t>
         </is>
       </c>
     </row>
@@ -17926,10 +18202,11 @@
       </c>
       <c r="G1384" t="inlineStr">
         <is>
-          <t>不易移動而導致滅絕。</t>
-        </is>
-      </c>
-    </row>
+          <t>行動不便而導致滅絕。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385"/>
     <row r="1386">
       <c r="B1386" t="inlineStr">
         <is>
@@ -17978,6 +18255,7 @@
         </is>
       </c>
     </row>
+    <row r="1390"/>
     <row r="1391">
       <c r="A1391" t="inlineStr">
         <is>
@@ -18056,6 +18334,7 @@
         </is>
       </c>
     </row>
+    <row r="1395"/>
     <row r="1396">
       <c r="B1396" t="inlineStr">
         <is>
@@ -18104,6 +18383,7 @@
         </is>
       </c>
     </row>
+    <row r="1400"/>
     <row r="1401">
       <c r="A1401" t="inlineStr">
         <is>
@@ -18182,6 +18462,7 @@
         </is>
       </c>
     </row>
+    <row r="1405"/>
     <row r="1406">
       <c r="B1406" t="inlineStr">
         <is>
@@ -18230,6 +18511,7 @@
         </is>
       </c>
     </row>
+    <row r="1410"/>
     <row r="1411">
       <c r="A1411" t="inlineStr">
         <is>
@@ -18308,6 +18590,7 @@
         </is>
       </c>
     </row>
+    <row r="1415"/>
     <row r="1416">
       <c r="B1416" t="inlineStr">
         <is>
@@ -18356,6 +18639,7 @@
         </is>
       </c>
     </row>
+    <row r="1420"/>
     <row r="1421">
       <c r="A1421" t="inlineStr">
         <is>
@@ -18434,6 +18718,7 @@
         </is>
       </c>
     </row>
+    <row r="1425"/>
     <row r="1426">
       <c r="B1426" t="inlineStr">
         <is>
@@ -18482,6 +18767,7 @@
         </is>
       </c>
     </row>
+    <row r="1430"/>
     <row r="1431">
       <c r="A1431" t="inlineStr">
         <is>
@@ -18534,7 +18820,7 @@
       </c>
       <c r="G1433" t="inlineStr">
         <is>
-          <t>日空中的空氣中含有的</t>
+          <t>冬天空氣中的水分凍結，</t>
         </is>
       </c>
     </row>
@@ -18556,10 +18842,11 @@
       </c>
       <c r="G1434" t="inlineStr">
         <is>
-          <t>水分凍結，降下雪花。</t>
-        </is>
-      </c>
-    </row>
+          <t>讓雪花降下。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435"/>
     <row r="1436">
       <c r="B1436" t="inlineStr">
         <is>
@@ -18608,6 +18895,7 @@
         </is>
       </c>
     </row>
+    <row r="1440"/>
     <row r="1441">
       <c r="A1441" t="inlineStr">
         <is>
@@ -18686,6 +18974,7 @@
         </is>
       </c>
     </row>
+    <row r="1445"/>
     <row r="1446">
       <c r="B1446" t="inlineStr">
         <is>
@@ -18734,6 +19023,7 @@
         </is>
       </c>
     </row>
+    <row r="1450"/>
     <row r="1451">
       <c r="A1451" t="inlineStr">
         <is>
@@ -18786,7 +19076,7 @@
       </c>
       <c r="G1453" t="inlineStr">
         <is>
-          <t>起劇烈燃燒著的雙翅，</t>
+          <t>熊熊燃燒的雙翅，</t>
         </is>
       </c>
     </row>
@@ -18808,10 +19098,11 @@
       </c>
       <c r="G1454" t="inlineStr">
         <is>
-          <t>哪怕是夜空也會被點亮。</t>
-        </is>
-      </c>
-    </row>
+          <t>連夜空都會被映紅。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455"/>
     <row r="1456">
       <c r="B1456" t="inlineStr">
         <is>
@@ -18860,6 +19151,7 @@
         </is>
       </c>
     </row>
+    <row r="1460"/>
     <row r="1461">
       <c r="A1461" t="inlineStr">
         <is>
@@ -18890,7 +19182,7 @@
       </c>
       <c r="G1462" t="inlineStr">
         <is>
-          <t>本被認為只存於幻想之中，</t>
+          <t>曾被認為是幻想。</t>
         </is>
       </c>
     </row>
@@ -18912,7 +19204,7 @@
       </c>
       <c r="G1463" t="inlineStr">
         <is>
-          <t>直到最近有人將它釣起，</t>
+          <t>直到最近被釣到後，</t>
         </is>
       </c>
     </row>
@@ -18934,10 +19226,11 @@
       </c>
       <c r="G1464" t="inlineStr">
         <is>
-          <t>它的存在才得到了證實。</t>
-        </is>
-      </c>
-    </row>
+          <t>才證實其存在。</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465"/>
     <row r="1466">
       <c r="B1466" t="inlineStr">
         <is>
@@ -18986,6 +19279,7 @@
         </is>
       </c>
     </row>
+    <row r="1470"/>
     <row r="1471">
       <c r="A1471" t="inlineStr">
         <is>
@@ -19064,6 +19358,7 @@
         </is>
       </c>
     </row>
+    <row r="1475"/>
     <row r="1476">
       <c r="B1476" t="inlineStr">
         <is>
@@ -19112,6 +19407,7 @@
         </is>
       </c>
     </row>
+    <row r="1480"/>
     <row r="1481">
       <c r="A1481" t="inlineStr">
         <is>
@@ -19164,7 +19460,7 @@
       </c>
       <c r="G1483" t="inlineStr">
         <is>
-          <t>某個地方，靠飛行來移動。</t>
+          <t>某個地方，並且會飛行。</t>
         </is>
       </c>
     </row>
@@ -19190,6 +19486,7 @@
         </is>
       </c>
     </row>
+    <row r="1485"/>
     <row r="1486">
       <c r="B1486" t="inlineStr">
         <is>
@@ -19238,6 +19535,7 @@
         </is>
       </c>
     </row>
+    <row r="1490"/>
     <row r="1491">
       <c r="A1491" t="inlineStr">
         <is>
@@ -19316,6 +19614,7 @@
         </is>
       </c>
     </row>
+    <row r="1495"/>
     <row r="1496">
       <c r="B1496" t="inlineStr">
         <is>
@@ -19364,6 +19663,7 @@
         </is>
       </c>
     </row>
+    <row r="1500"/>
     <row r="1501">
       <c r="A1501" t="inlineStr">
         <is>
@@ -19442,6 +19742,7 @@
         </is>
       </c>
     </row>
+    <row r="1505"/>
     <row r="1506">
       <c r="B1506" t="inlineStr">
         <is>
